--- a/KaggleChallenge2/exps/note_challenge2.xlsx
+++ b/KaggleChallenge2/exps/note_challenge2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
   <si>
     <t>Thời gian thực hiện</t>
   </si>
@@ -224,6 +224,24 @@
   </si>
   <si>
     <t>Thêm mô hình GradientBoosting giúp tăng hiệu suất.</t>
+  </si>
+  <si>
+    <t>31/10, 13h29</t>
+  </si>
+  <si>
+    <t>Xóa đặc trưng MoSold, dùng kỹ thuật mô hình ở (23)</t>
+  </si>
+  <si>
+    <t>Xóa MoSold giúp tăng hiệu suất mô hình</t>
+  </si>
+  <si>
+    <t>1/11, 18h53</t>
+  </si>
+  <si>
+    <t>Sửa lại tham số mô hình GradientBoost với n_estimators = 2000</t>
+  </si>
+  <si>
+    <t>Sửa lại tham số giúp tăng nhẹ hiệu suất mô hình</t>
   </si>
 </sst>
 </file>
@@ -538,6 +556,7 @@
       <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="F3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="3">
@@ -945,6 +964,40 @@
       </c>
       <c r="E26" s="11" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>24.0</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.11908</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.11903</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
